--- a/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que duermen las horas recomendadas en función de su edad</t>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,75; 84,34</t>
+          <t>73,33; 84,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,16; 82,64</t>
+          <t>70,37; 82,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,81; 85,18</t>
+          <t>73,87; 85,34</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>64,71; 77,44</t>
+          <t>65,33; 77,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,1; 83,45</t>
+          <t>72,9; 83,28</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,99; 77,19</t>
+          <t>64,98; 77,55</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>63,86; 76,78</t>
+          <t>64,4; 76,64</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>62,6; 79,42</t>
+          <t>63,56; 79,3</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,92; 82,48</t>
+          <t>74,26; 82,43</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,66; 78,56</t>
+          <t>70,02; 78,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70,67; 79,31</t>
+          <t>70,84; 79,36</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,2; 77,17</t>
+          <t>66,39; 76,77</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,24; 81,4</t>
+          <t>72,17; 81,54</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,21; 77,65</t>
+          <t>68,3; 77,77</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>58,84; 69,24</t>
+          <t>59,42; 69,55</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,99; 78,41</t>
+          <t>67,72; 78,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,18; 82,35</t>
+          <t>73,31; 82,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,16; 76,15</t>
+          <t>66,48; 76,25</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,11; 69,48</t>
+          <t>59,52; 69,61</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>65,64; 76,42</t>
+          <t>66,16; 76,09</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,08; 80,89</t>
+          <t>74,17; 80,52</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,81; 75,58</t>
+          <t>68,45; 75,66</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,68; 68,04</t>
+          <t>60,69; 68,06</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,71; 76,04</t>
+          <t>68,31; 75,98</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,43; 72,29</t>
+          <t>60,02; 72,45</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>59,98; 71,9</t>
+          <t>60,18; 72,26</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,53; 72,31</t>
+          <t>61,41; 73,13</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,94; 84,53</t>
+          <t>67,17; 84,0</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,94; 77,36</t>
+          <t>65,93; 77,35</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,01; 77,2</t>
+          <t>66,54; 77,36</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,65; 71,52</t>
+          <t>59,55; 71,86</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,99; 73,3</t>
+          <t>58,7; 73,17</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65,05; 73,51</t>
+          <t>64,66; 73,19</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>65,4; 73,1</t>
+          <t>64,93; 73,3</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,01; 70,63</t>
+          <t>62,63; 70,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,03; 77,3</t>
+          <t>65,1; 77,3</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>66,04; 76,24</t>
+          <t>65,73; 76,78</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,36; 77,16</t>
+          <t>66,23; 77,2</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,21; 72,6</t>
+          <t>60,95; 72,1</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,99; 70,59</t>
+          <t>57,71; 70,17</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,84; 73,48</t>
+          <t>62,88; 73,16</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,49; 76,01</t>
+          <t>65,42; 76,19</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,8; 72,72</t>
+          <t>61,8; 72,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>62,75; 75,56</t>
+          <t>63,19; 75,71</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,17; 73,29</t>
+          <t>66,06; 73,59</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,56; 75,41</t>
+          <t>67,54; 74,97</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>62,98; 70,93</t>
+          <t>63,1; 71,34</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,73; 71,15</t>
+          <t>62,33; 71,3</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>71,17; 76,38</t>
+          <t>70,72; 76,19</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,15; 74,47</t>
+          <t>69,04; 74,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,6</t>
+          <t>65,99; 71,57</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>68,0; 75,21</t>
+          <t>67,77; 75,28</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,33; 76,62</t>
+          <t>71,13; 76,45</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,11</t>
+          <t>68,83; 74,39</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,18; 69,86</t>
+          <t>64,22; 69,79</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,64; 73,23</t>
+          <t>66,24; 72,64</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,97; 75,8</t>
+          <t>71,92; 75,71</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,71; 73,46</t>
+          <t>69,93; 73,84</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,75; 69,67</t>
+          <t>65,38; 69,51</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,74; 72,85</t>
+          <t>67,87; 72,87</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que duermen las horas recomendadas en función de su edad (tasa de respuesta: 99,43%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>&lt;10.000 hab</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>284</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>108670</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>107177</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>106802</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>82276</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>118944</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>110222</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>105031</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>99299</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>227614</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>217399</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>211833</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>181576</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>100268; 116001</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>98066; 114949</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>98767; 114100</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>75257; 89449</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>110604; 126360</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100081; 119445</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>95360; 113484</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>88227; 110076</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>214210; 237780</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>205414; 230137</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>199603; 223634</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>168640; 195003</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>10-50.000 hab</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>491</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>460</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>426</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>429</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>150293</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>150691</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>132710</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>139833</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>164884</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>159574</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>144842</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>182355</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>315177</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>310265</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>277552</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>322189</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>140382; 158605</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>140940; 160478</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>122487; 143366</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>129021; 149491</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>155016; 173812</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>148355; 170170</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>133166; 155742</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>168742; 194046</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>301099; 326880</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>294006; 324979</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>260897; 292574</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>304337; 338525</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>&gt;50.000 hab</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>311</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>344</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>329</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>296</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>90777</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>102626</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>102938</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>140656</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>107097</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>120089</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>108402</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>122336</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>197873</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>222715</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>211341</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>262992</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>82170; 99193</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>93102; 111779</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>94199; 112177</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>126145; 157739</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>98354; 115384</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>110847; 128872</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97893; 118113</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>108534; 135289</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>184988; 209370</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>208620; 235496</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>199020; 224784</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>242609; 288096</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Capitales</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>397</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>379</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>314</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>147432</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>150457</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>138144</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>106720</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>141443</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>148069</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>136001</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>126382</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>288875</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>298527</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>274145</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>233103</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>136057; 158934</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>138767; 161735</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>125559; 148532</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>95883; 116596</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>130250; 151546</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>136336; 158768</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>124876; 147211</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>114529; 137207</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>273582; 304756</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>282248; 313317</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>257479; 291108</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>216535; 247676</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>737</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>731</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>630</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>1535</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>1497</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>1418</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>1282</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>497172</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>510951</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>480594</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>469486</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>530373</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>1029540</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>1048906</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>974870</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>999859</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>477467; 514381</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>490168; 529356</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>461446; 500446</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>447035; 496594</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>511759; 550048</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>517703; 559539</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>474082; 515200</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>503401; 552053</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1003068; 1055854</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>1022475; 1079630</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>939878; 999255</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>963471; 1034488</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>73,33; 84,84</t>
+          <t>74,09; 84,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,37; 82,48</t>
+          <t>70,87; 82,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,87; 85,34</t>
+          <t>73,74; 85,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,33; 77,65</t>
+          <t>65,4; 77,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>72,9; 83,28</t>
+          <t>73,07; 83,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>64,98; 77,55</t>
+          <t>65,53; 77,63</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>64,4; 76,64</t>
+          <t>65,0; 77,09</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,56; 79,3</t>
+          <t>63,17; 79,39</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,26; 82,43</t>
+          <t>74,67; 82,37</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>70,02; 78,45</t>
+          <t>69,88; 78,03</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70,84; 79,36</t>
+          <t>70,48; 79,14</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,39; 76,77</t>
+          <t>66,33; 76,85</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,17; 81,54</t>
+          <t>72,42; 81,4</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>68,3; 77,77</t>
+          <t>67,89; 77,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,42; 69,55</t>
+          <t>59,03; 69,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,72; 78,47</t>
+          <t>67,45; 78,47</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,31; 82,2</t>
+          <t>73,14; 82,09</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,48; 76,25</t>
+          <t>66,11; 75,91</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,52; 69,61</t>
+          <t>59,39; 69,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,16; 76,09</t>
+          <t>66,23; 76,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,17; 80,52</t>
+          <t>74,18; 80,95</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,45; 75,66</t>
+          <t>68,79; 75,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,69; 68,06</t>
+          <t>60,7; 68,35</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,31; 75,98</t>
+          <t>68,47; 75,81</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,02; 72,45</t>
+          <t>60,12; 72,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>60,18; 72,26</t>
+          <t>61,11; 72,74</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,41; 73,13</t>
+          <t>60,9; 72,32</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>67,17; 84,0</t>
+          <t>66,81; 84,25</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,93; 77,35</t>
+          <t>65,75; 77,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,54; 77,36</t>
+          <t>66,26; 77,38</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,55; 71,86</t>
+          <t>59,98; 72,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,7; 73,17</t>
+          <t>58,71; 72,63</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,66; 73,19</t>
+          <t>64,77; 73,41</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,93; 73,3</t>
+          <t>64,97; 73,03</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,63; 70,74</t>
+          <t>62,05; 70,83</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,1; 77,3</t>
+          <t>65,36; 77,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,73; 76,78</t>
+          <t>65,56; 76,39</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>66,23; 77,2</t>
+          <t>65,97; 76,86</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>60,95; 72,1</t>
+          <t>61,28; 72,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,71; 70,17</t>
+          <t>57,41; 70,37</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,88; 73,16</t>
+          <t>62,97; 73,34</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,42; 76,19</t>
+          <t>65,51; 75,98</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,8; 72,86</t>
+          <t>61,12; 72,56</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,19; 75,71</t>
+          <t>63,16; 74,95</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,06; 73,59</t>
+          <t>66,19; 73,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,54; 74,97</t>
+          <t>67,53; 74,83</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,1; 71,34</t>
+          <t>63,24; 70,95</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,33; 71,3</t>
+          <t>62,64; 71,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,72; 76,19</t>
+          <t>70,92; 76,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,04; 74,56</t>
+          <t>69,23; 74,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,99; 71,57</t>
+          <t>65,55; 71,16</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,77; 75,28</t>
+          <t>67,89; 75,15</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,13; 76,45</t>
+          <t>71,44; 76,49</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,83; 74,39</t>
+          <t>68,73; 74,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,22; 69,79</t>
+          <t>64,03; 69,81</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,24; 72,64</t>
+          <t>66,35; 72,98</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,92; 75,71</t>
+          <t>71,91; 75,67</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,93; 73,84</t>
+          <t>69,76; 73,73</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,38; 69,51</t>
+          <t>65,79; 69,72</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>67,87; 72,87</t>
+          <t>68,15; 72,75</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>100268; 116001</t>
+          <t>101301; 115693</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98066; 114949</t>
+          <t>98760; 115276</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98767; 114100</t>
+          <t>98601; 114221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75257; 89449</t>
+          <t>75336; 89582</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110604; 126360</t>
+          <t>110858; 127063</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100081; 119445</t>
+          <t>100925; 119556</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>95360; 113484</t>
+          <t>96250; 114155</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>88227; 110076</t>
+          <t>87689; 110209</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>214210; 237780</t>
+          <t>215379; 237591</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205414; 230137</t>
+          <t>205021; 228928</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199603; 223634</t>
+          <t>198590; 222992</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>168640; 195003</t>
+          <t>168474; 195201</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>140382; 158605</t>
+          <t>140867; 158328</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140940; 160478</t>
+          <t>140100; 159911</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>122487; 143366</t>
+          <t>121697; 143436</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>129021; 149491</t>
+          <t>128491; 149487</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>155016; 173812</t>
+          <t>154669; 173590</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>148355; 170170</t>
+          <t>147539; 169409</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>133166; 155742</t>
+          <t>132883; 155643</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168742; 194046</t>
+          <t>168907; 193958</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>301099; 326880</t>
+          <t>301144; 328619</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>294006; 324979</t>
+          <t>295464; 324177</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260897; 292574</t>
+          <t>260957; 293822</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>304337; 338525</t>
+          <t>305051; 337754</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82170; 99193</t>
+          <t>82304; 98946</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>93102; 111779</t>
+          <t>94535; 112535</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>94199; 112177</t>
+          <t>93412; 110926</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>126145; 157739</t>
+          <t>125472; 158208</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98354; 115384</t>
+          <t>98077; 115510</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110847; 128872</t>
+          <t>110383; 128908</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>97893; 118113</t>
+          <t>98594; 118485</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>108534; 135289</t>
+          <t>108542; 134291</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>184988; 209370</t>
+          <t>185304; 210021</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208620; 235496</t>
+          <t>208748; 234647</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>199020; 224784</t>
+          <t>197184; 225080</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>242609; 288096</t>
+          <t>243568; 289660</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>136057; 158934</t>
+          <t>135697; 158117</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138767; 161735</t>
+          <t>138212; 161041</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>125559; 148532</t>
+          <t>126247; 148862</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95883; 116596</t>
+          <t>95388; 116921</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130250; 151546</t>
+          <t>130431; 151904</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136336; 158768</t>
+          <t>136521; 158336</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>124876; 147211</t>
+          <t>123503; 146603</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>114529; 137207</t>
+          <t>114470; 135842</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>273582; 304756</t>
+          <t>274114; 303306</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>282248; 313317</t>
+          <t>282231; 312740</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>257479; 291108</t>
+          <t>258075; 289525</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>216535; 247676</t>
+          <t>217619; 247367</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>477467; 514381</t>
+          <t>478826; 515681</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>490168; 529356</t>
+          <t>491483; 531483</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>461446; 500446</t>
+          <t>458336; 497620</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447035; 496594</t>
+          <t>447861; 495758</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>511759; 550048</t>
+          <t>513998; 550329</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>517703; 559539</t>
+          <t>516931; 557348</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>474082; 515200</t>
+          <t>472693; 515355</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>503401; 552053</t>
+          <t>504217; 554632</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1003068; 1055854</t>
+          <t>1002908; 1055340</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1022475; 1079630</t>
+          <t>1019954; 1078025</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>939878; 999255</t>
+          <t>945678; 1002204</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>963471; 1034488</t>
+          <t>967512; 1032773</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/IQ23_R-Habitat-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>78,4%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>71,57%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>70,93%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>72,59%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>79,47%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>76,91%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>79,88%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>71,42%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>78,4%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,57%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>70,93%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>71,48%</t>
+          <t>72,55%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>74,09; 84,61</t>
+          <t>73,1; 83,45</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>70,87; 82,72</t>
+          <t>64,99; 77,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>73,74; 85,43</t>
+          <t>63,86; 76,78</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,4; 77,76</t>
+          <t>64,96; 79,6</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>73,07; 83,75</t>
+          <t>73,75; 84,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,53; 77,63</t>
+          <t>70,16; 82,64</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,0; 77,09</t>
+          <t>73,81; 85,18</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>63,17; 79,39</t>
+          <t>66,09; 78,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>74,67; 82,37</t>
+          <t>74,92; 82,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>69,88; 78,03</t>
+          <t>69,66; 78,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>70,48; 79,14</t>
+          <t>70,67; 79,31</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>66,33; 76,85</t>
+          <t>67,63; 78,01</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>77,98%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>71,5%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>64,74%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>73,24%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>77,27%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>73,02%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>64,38%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>73,4%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>77,98%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>71,5%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>64,74%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>73,32%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>72,42; 81,4</t>
+          <t>73,18; 82,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>67,89; 77,49</t>
+          <t>66,16; 76,15</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>59,03; 69,58</t>
+          <t>59,11; 69,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67,45; 78,47</t>
+          <t>67,47; 78,3</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>73,14; 82,09</t>
+          <t>72,24; 81,4</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>66,11; 75,91</t>
+          <t>68,21; 77,65</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>59,39; 69,57</t>
+          <t>58,84; 69,24</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>66,23; 76,05</t>
+          <t>67,89; 78,16</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>74,18; 80,95</t>
+          <t>74,08; 80,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68,79; 75,47</t>
+          <t>68,81; 75,58</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>60,7; 68,35</t>
+          <t>60,68; 68,04</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>68,47; 75,81</t>
+          <t>69,66; 76,65</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>71,79%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>72,09%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>65,95%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>66,99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>66,31%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>66,34%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>67,11%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>74,9%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>71,79%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>72,09%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>65,95%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>70,57%</t>
+          <t>69,38%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>60,12; 72,27</t>
+          <t>65,94; 77,36</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>61,11; 72,74</t>
+          <t>66,01; 77,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,9; 72,32</t>
+          <t>59,65; 71,52</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>66,81; 84,25</t>
+          <t>59,71; 73,98</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>65,75; 77,43</t>
+          <t>60,43; 72,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>66,26; 77,38</t>
+          <t>59,98; 71,9</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>59,98; 72,08</t>
+          <t>60,53; 72,31</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>58,71; 72,63</t>
+          <t>65,74; 77,25</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>64,77; 73,41</t>
+          <t>65,05; 73,51</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>64,97; 73,03</t>
+          <t>65,4; 73,1</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>62,05; 70,83</t>
+          <t>62,01; 70,63</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>65,36; 77,72</t>
+          <t>63,82; 73,6</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>68,29%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>71,05%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>67,31%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>70,56%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>71,23%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>71,81%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>67,06%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>64,23%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>68,29%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>71,05%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>67,31%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>66,35%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>68,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>65,56; 76,39</t>
+          <t>62,84; 73,48</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>65,97; 76,86</t>
+          <t>65,49; 76,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61,28; 72,26</t>
+          <t>61,8; 72,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57,41; 70,37</t>
+          <t>64,03; 76,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>62,97; 73,34</t>
+          <t>66,04; 76,24</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>65,51; 75,98</t>
+          <t>66,36; 77,16</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>61,12; 72,56</t>
+          <t>61,21; 72,6</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>63,16; 74,95</t>
+          <t>60,26; 72,56</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,19; 73,24</t>
+          <t>66,17; 73,29</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67,53; 74,83</t>
+          <t>67,56; 75,41</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>63,24; 70,95</t>
+          <t>62,98; 70,93</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,64; 71,21</t>
+          <t>64,18; 72,56</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>73,99%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>71,52%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>66,95%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>70,97%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>73,64%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>71,97%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>68,73%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>71,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>73,99%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>71,52%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>66,95%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>71,02%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,99%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>70,92; 76,38</t>
+          <t>71,33; 76,62</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>69,23; 74,86</t>
+          <t>68,73; 74,11</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65,55; 71,16</t>
+          <t>64,18; 69,86</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>67,89; 75,15</t>
+          <t>67,79; 74,24</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>71,44; 76,49</t>
+          <t>71,17; 76,38</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>68,73; 74,1</t>
+          <t>69,15; 74,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>64,03; 69,81</t>
+          <t>65,99; 71,6</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>66,35; 72,98</t>
+          <t>68,09; 73,85</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>71,91; 75,67</t>
+          <t>71,97; 75,8</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>69,76; 73,73</t>
+          <t>69,71; 73,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,79; 69,72</t>
+          <t>65,75; 69,67</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>68,15; 72,75</t>
+          <t>68,42; 73,08</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1509,42 +1509,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>157</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>146</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>148</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>131</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>136</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1577,42 +1577,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>118944</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>110222</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>105031</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>90228</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>108670</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>107177</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>106802</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>82276</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>118944</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>110222</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>105031</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>99299</t>
+          <t>86551</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>181576</t>
+          <t>176779</t>
         </is>
       </c>
     </row>
@@ -1645,62 +1645,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>101301; 115693</t>
+          <t>110913; 126611</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>98760; 115276</t>
+          <t>100092; 118888</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>98601; 114221</t>
+          <t>94558; 113699</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>75336; 89582</t>
+          <t>80741; 98941</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>110858; 127063</t>
+          <t>100848; 115322</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>100925; 119556</t>
+          <t>97772; 115158</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96250; 114155</t>
+          <t>98686; 113894</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87689; 110209</t>
+          <t>78886; 93803</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>215379; 237591</t>
+          <t>216125; 237917</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>205021; 228928</t>
+          <t>204369; 230486</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>198590; 222992</t>
+          <t>199123; 223492</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>168474; 195201</t>
+          <t>164786; 190071</t>
         </is>
       </c>
     </row>
@@ -1717,42 +1717,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>240</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>230</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>212</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>196</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>251</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>230</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>214</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>233</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1785,42 +1785,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>164884</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>159574</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>144842</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>173724</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>150293</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>150691</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>132710</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>139833</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>164884</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>159574</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>144842</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>182355</t>
+          <t>135402</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>322189</t>
+          <t>309126</t>
         </is>
       </c>
     </row>
@@ -1853,62 +1853,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>140867; 158328</t>
+          <t>154748; 174139</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>140100; 159911</t>
+          <t>147642; 169932</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>121697; 143436</t>
+          <t>132242; 155451</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>128491; 149487</t>
+          <t>160050; 185721</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>154669; 173590</t>
+          <t>140507; 158322</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>147539; 169409</t>
+          <t>140759; 160229</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>132883; 155643</t>
+          <t>121304; 142733</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168907; 193958</t>
+          <t>125204; 144135</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>301144; 328619</t>
+          <t>300733; 328373</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>295464; 324177</t>
+          <t>295546; 324617</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>260957; 293822</t>
+          <t>260853; 292481</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>305051; 337754</t>
+          <t>293710; 323151</t>
         </is>
       </c>
     </row>
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>159</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>169</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>153</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>163</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>160</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>143</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,42 +1993,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>107097</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>120089</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>108402</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>112567</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>90777</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>102626</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>102938</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>140656</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>107097</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>120089</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>108402</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>122336</t>
+          <t>111170</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2048,7 +2048,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>262992</t>
+          <t>223737</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>82304; 98946</t>
+          <t>98369; 115406</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>94535; 112535</t>
+          <t>109969; 128609</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>93412; 110926</t>
+          <t>98051; 117568</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>125472; 158208</t>
+          <t>100332; 124312</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>98077; 115510</t>
+          <t>82738; 98974</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>110383; 128908</t>
+          <t>92792; 111223</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>98594; 118485</t>
+          <t>92844; 110911</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>108542; 134291</t>
+          <t>101534; 119308</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>185304; 210021</t>
+          <t>186084; 210284</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>208748; 234647</t>
+          <t>210135; 234863</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>197184; 225080</t>
+          <t>197052; 224429</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>243568; 289660</t>
+          <t>205806; 237345</t>
         </is>
       </c>
     </row>
@@ -2133,42 +2133,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
           <t>192</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>196</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>187</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>150</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>201</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>164</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>141443</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>148069</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>136001</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>119511</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>147432</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>150457</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>138144</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>106720</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>141443</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>148069</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>136001</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>126382</t>
+          <t>109611</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>233103</t>
+          <t>229122</t>
         </is>
       </c>
     </row>
@@ -2269,62 +2269,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>135697; 158117</t>
+          <t>130160; 152197</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>138212; 161041</t>
+          <t>136477; 158396</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>126247; 148862</t>
+          <t>124865; 146939</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>95388; 116921</t>
+          <t>108459; 129431</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>130431; 151904</t>
+          <t>136687; 157802</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>136521; 158336</t>
+          <t>139040; 161653</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>123503; 146603</t>
+          <t>126094; 149565</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>114470; 135842</t>
+          <t>99551; 119865</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>274114; 303306</t>
+          <t>274009; 303502</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>282231; 312740</t>
+          <t>282344; 315155</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>258075; 289525</t>
+          <t>257011; 289459</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>217619; 247367</t>
+          <t>214723; 242758</t>
         </is>
       </c>
     </row>
@@ -2341,42 +2341,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>798</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>766</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>652</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>737</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>731</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>716</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>630</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>798</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>766</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>652</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2409,42 +2409,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>532368</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>537955</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>494276</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>496031</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>497172</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>510951</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>480594</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>469486</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>532368</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>537955</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>494276</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>530373</t>
+          <t>442733</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>999859</t>
+          <t>938765</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>478826; 515681</t>
+          <t>513235; 551237</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>491483; 531483</t>
+          <t>516946; 557406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>458336; 497620</t>
+          <t>473777; 515717</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>447861; 495758</t>
+          <t>473783; 518880</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>513998; 550329</t>
+          <t>480522; 515664</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>516931; 557348</t>
+          <t>490900; 528676</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>472693; 515355</t>
+          <t>461458; 500683</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>504217; 554632</t>
+          <t>424474; 460390</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1002908; 1055340</t>
+          <t>1003723; 1057093</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>1019954; 1078025</t>
+          <t>1019157; 1074094</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>945678; 1002204</t>
+          <t>945109; 1001563</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>967512; 1032773</t>
+          <t>904712; 966284</t>
         </is>
       </c>
     </row>
